--- a/commission/karin/2026-07.xlsx
+++ b/commission/karin/2026-07.xlsx
@@ -52,7 +52,7 @@
     <t>✗ MISSED — Standard waterfall</t>
   </si>
   <si>
-    <t>Fallback: standard 5% / 6% / 7.5% / 10% waterfall on $14,400 collected</t>
+    <t>Fallback: standard 5% / 6% / 7.5% / 10% waterfall on $16,800 collected</t>
   </si>
   <si>
     <t>Account / Date</t>
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>900</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -753,7 +753,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="11">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1047,10 +1047,10 @@
         <v>46</v>
       </c>
       <c r="F32" s="29">
-        <v>18000</v>
+        <v>20400</v>
       </c>
       <c r="H32" s="30">
-        <v>900</v>
+        <v>1020</v>
       </c>
     </row>
   </sheetData>

--- a/commission/karin/2026-07.xlsx
+++ b/commission/karin/2026-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -97,6 +97,12 @@
     <t>ORD-EPL-1127</t>
   </si>
   <si>
+    <t>Elgin Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1144</t>
+  </si>
+  <si>
     <t>Panorama Equine Medical and Surgical Center</t>
   </si>
   <si>
@@ -110,6 +116,12 @@
   </si>
   <si>
     <t>ORD-EPL-1140</t>
+  </si>
+  <si>
+    <t>113 Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1137</t>
   </si>
   <si>
     <t>ADJUSTMENTS</t>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -877,7 +889,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="17">
-        <v>46225.5</v>
+        <v>46224.5</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>23</v>
@@ -886,44 +898,44 @@
         <v>29</v>
       </c>
       <c r="F18" s="19">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="G18" s="20">
         <v>0.05</v>
       </c>
       <c r="H18" s="21">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="17">
-        <v>46232.5</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="F20" s="15">
+        <v>1800</v>
+      </c>
+      <c r="H20" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="17">
+        <v>46225.5</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="19">
+        <v>600</v>
+      </c>
+      <c r="G21" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H21" s="21">
         <v>30</v>
-      </c>
-      <c r="F19" s="19">
-        <v>1200</v>
-      </c>
-      <c r="G19" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="H19" s="21">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="15">
-        <v>1800</v>
-      </c>
-      <c r="H21" s="16">
-        <v>90</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
@@ -937,119 +949,181 @@
         <v>32</v>
       </c>
       <c r="F22" s="19">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="G22" s="20">
         <v>0.05</v>
       </c>
       <c r="H22" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="15">
+        <v>1800</v>
+      </c>
+      <c r="H24" s="16">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
-        <v>33</v>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="17">
+        <v>46232.5</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="19">
+        <v>1800</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="21">
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="23" t="s">
+      <c r="A27" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="15">
+        <v>600</v>
+      </c>
+      <c r="H27" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="17">
+        <v>46219.5</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F28" s="19">
         <v>600</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G28" s="20">
         <v>0.05</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H28" s="21">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="23" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="5" t="s">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="24">
+      <c r="D33" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="24">
         <v>600</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G33" s="25">
         <v>0.05</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H33" s="24">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="5" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="24">
+      <c r="E34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="24">
+        <v>600</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="H34" s="24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="24">
         <v>1800</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G35" s="25">
         <v>0.05</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H35" s="24">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="24">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="24">
         <v>600</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G36" s="25">
         <v>0.05</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H36" s="24">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="27">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="27">
         <v>3600</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H37" s="27">
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="29">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="29">
         <v>20400</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H38" s="30">
         <v>1020</v>
       </c>
     </row>

--- a/commission/karin/2026-07.xlsx
+++ b/commission/karin/2026-07.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="July 2026-07" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Invoiced This Month" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -164,6 +165,90 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Invoiced This Month — Karin Williamson — July 2026</t>
+  </si>
+  <si>
+    <t>Every invoice you wrote this month (paid or unpaid). Commission math comes from Tab 1 — this sheet is for visibility only.</t>
+  </si>
+  <si>
+    <t>INV#</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vials</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Commissionable</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Open Bal</t>
+  </si>
+  <si>
+    <t>Promo</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ORD-EPL-1134</t>
+  </si>
+  <si>
+    <t>Austin Equine</t>
+  </si>
+  <si>
+    <t>EMTNSTUDY</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1135</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1143</t>
+  </si>
+  <si>
+    <t>Northwest Equine Performance</t>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1148</t>
+  </si>
+  <si>
+    <t>Buffalo Veterinary Clinic PC</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1147</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1151</t>
+  </si>
+  <si>
+    <t>Perfect Balance Equine Dentistry and Veterinary Services</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1150</t>
+  </si>
+  <si>
+    <t>12 invoices</t>
   </si>
 </sst>
 </file>
@@ -176,7 +261,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -263,6 +348,42 @@
     <font>
       <b/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <color rgb="7A7974"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="7A7974"/>
     </font>
   </fonts>
   <fills count="4">
@@ -295,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -349,6 +470,45 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1131,4 +1291,565 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="34">
+        <v>46204.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="35">
+        <v>3</v>
+      </c>
+      <c r="E6" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F6" s="36">
+        <v>675</v>
+      </c>
+      <c r="G6" s="37">
+        <v>1800</v>
+      </c>
+      <c r="H6" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I6" s="21">
+        <v>1800</v>
+      </c>
+      <c r="J6" s="34">
+        <v>46254.5</v>
+      </c>
+      <c r="K6" s="38">
+        <v>0</v>
+      </c>
+      <c r="L6" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="34">
+        <v>46209.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="35">
+        <v>3</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1275</v>
+      </c>
+      <c r="F7" s="36">
+        <v>1275</v>
+      </c>
+      <c r="G7" s="37">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
+        <v>0</v>
+      </c>
+      <c r="I7" s="38">
+        <v>0</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="38">
+        <v>0</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="34">
+        <v>46210.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="35">
+        <v>2</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F8" s="36">
+        <v>375</v>
+      </c>
+      <c r="G8" s="37">
+        <v>1275</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1200</v>
+      </c>
+      <c r="I8" s="21">
+        <v>1275</v>
+      </c>
+      <c r="J8" s="34">
+        <v>46232.5</v>
+      </c>
+      <c r="K8" s="38">
+        <v>0</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="34">
+        <v>46210.5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="35">
+        <v>3</v>
+      </c>
+      <c r="E9" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F9" s="36">
+        <v>675</v>
+      </c>
+      <c r="G9" s="37">
+        <v>1800</v>
+      </c>
+      <c r="H9" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1800</v>
+      </c>
+      <c r="J9" s="34">
+        <v>46254.5</v>
+      </c>
+      <c r="K9" s="38">
+        <v>0</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="34">
+        <v>46211.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="35">
+        <v>1</v>
+      </c>
+      <c r="E10" s="19">
+        <v>825</v>
+      </c>
+      <c r="F10" s="36">
+        <v>225</v>
+      </c>
+      <c r="G10" s="37">
+        <v>600</v>
+      </c>
+      <c r="H10" s="19">
+        <v>600</v>
+      </c>
+      <c r="I10" s="21">
+        <v>600</v>
+      </c>
+      <c r="J10" s="34">
+        <v>46219.5</v>
+      </c>
+      <c r="K10" s="38">
+        <v>0</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="34">
+        <v>46218.5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="35">
+        <v>3</v>
+      </c>
+      <c r="E11" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F11" s="36">
+        <v>675</v>
+      </c>
+      <c r="G11" s="37">
+        <v>1800</v>
+      </c>
+      <c r="H11" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I11" s="21">
+        <v>1853.82</v>
+      </c>
+      <c r="J11" s="34">
+        <v>46232.5</v>
+      </c>
+      <c r="K11" s="38">
+        <v>0</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="34">
+        <v>46223.5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="35">
+        <v>2</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F12" s="36">
+        <v>1650</v>
+      </c>
+      <c r="G12" s="37">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38">
+        <v>0</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="38">
+        <v>0</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="34">
+        <v>46224.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="35">
+        <v>3</v>
+      </c>
+      <c r="E13" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F13" s="36">
+        <v>675</v>
+      </c>
+      <c r="G13" s="37">
+        <v>1800</v>
+      </c>
+      <c r="H13" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I13" s="21">
+        <v>1800</v>
+      </c>
+      <c r="J13" s="34">
+        <v>46224.5</v>
+      </c>
+      <c r="K13" s="38">
+        <v>0</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="34">
+        <v>46225.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="35">
+        <v>2</v>
+      </c>
+      <c r="E14" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F14" s="36">
+        <v>450</v>
+      </c>
+      <c r="G14" s="37">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="19">
+        <v>1200</v>
+      </c>
+      <c r="I14" s="21">
+        <v>1200</v>
+      </c>
+      <c r="J14" s="34">
+        <v>46244.5</v>
+      </c>
+      <c r="K14" s="38">
+        <v>0</v>
+      </c>
+      <c r="L14" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="34">
+        <v>46225.5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="35">
+        <v>4</v>
+      </c>
+      <c r="E15" s="19">
+        <v>1700</v>
+      </c>
+      <c r="F15" s="36">
+        <v>1700</v>
+      </c>
+      <c r="G15" s="37">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0</v>
+      </c>
+      <c r="I15" s="38">
+        <v>0</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="38">
+        <v>0</v>
+      </c>
+      <c r="L15" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="34">
+        <v>46226.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="35">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F16" s="36">
+        <v>1650</v>
+      </c>
+      <c r="G16" s="37">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0</v>
+      </c>
+      <c r="I16" s="38">
+        <v>0</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="38">
+        <v>0</v>
+      </c>
+      <c r="L16" s="39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="34">
+        <v>46226.5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="35">
+        <v>8</v>
+      </c>
+      <c r="E17" s="19">
+        <v>6600</v>
+      </c>
+      <c r="F17" s="36">
+        <v>1800</v>
+      </c>
+      <c r="G17" s="37">
+        <v>4800</v>
+      </c>
+      <c r="H17" s="19">
+        <v>4800</v>
+      </c>
+      <c r="I17" s="21">
+        <v>4943.52</v>
+      </c>
+      <c r="J17" s="34">
+        <v>46239.5</v>
+      </c>
+      <c r="K17" s="38">
+        <v>0</v>
+      </c>
+      <c r="L17" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="41">
+        <v>36</v>
+      </c>
+      <c r="E19" s="37">
+        <v>26900</v>
+      </c>
+      <c r="F19" s="42">
+        <v>11825</v>
+      </c>
+      <c r="G19" s="43">
+        <v>15075</v>
+      </c>
+      <c r="H19" s="37">
+        <v>15000</v>
+      </c>
+      <c r="I19" s="44">
+        <v>15272.34</v>
+      </c>
+      <c r="K19" s="45">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>